--- a/data/dividends_info_20260724.xlsx
+++ b/data/dividends_info_20260724.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.93500137329102</v>
+        <v>46.76499938964844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1877542451686405</v>
+        <v>0.1924516223129081</v>
       </c>
       <c r="J2" t="n">
         <v>234</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.94999694824219</v>
+        <v>65.25</v>
       </c>
       <c r="I3" t="n">
-        <v>1.077752167652634</v>
+        <v>1.0727969348659</v>
       </c>
       <c r="J3" t="n">
         <v>213</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.100000381469727</v>
+        <v>9.159999847412109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.6550218449725329</v>
       </c>
       <c r="J4" t="n">
         <v>143</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.93500137329102</v>
+        <v>46.76499938964844</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1877542451686405</v>
+        <v>0.1924516223129081</v>
       </c>
       <c r="J6" t="n">
         <v>143</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.049999952316284</v>
+        <v>2.039999961853027</v>
       </c>
       <c r="I7" t="n">
-        <v>3.756097648343753</v>
+        <v>3.774509874503002</v>
       </c>
       <c r="J7" t="n">
         <v>122</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.72999954223633</v>
+        <v>22.95999908447266</v>
       </c>
       <c r="I8" t="n">
-        <v>1.187857481027629</v>
+        <v>1.175958235044509</v>
       </c>
       <c r="J8" t="n">
         <v>122</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.019999980926514</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="I9" t="n">
-        <v>3.322259146738715</v>
+        <v>3.350083869828403</v>
       </c>
       <c r="J9" t="n">
         <v>115</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.5</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.7894736941171157</v>
       </c>
       <c r="J10" t="n">
         <v>87</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.72999954223633</v>
+        <v>22.95999908447266</v>
       </c>
       <c r="I14" t="n">
-        <v>1.187857481027629</v>
+        <v>1.175958235044509</v>
       </c>
       <c r="J14" t="n">
         <v>59</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>47.93500137329102</v>
+        <v>46.76499938964844</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1877542451686405</v>
+        <v>0.1924516223129081</v>
       </c>
       <c r="J15" t="n">
         <v>59</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>91.44999694824219</v>
+        <v>92.25</v>
       </c>
       <c r="I16" t="n">
-        <v>1.454346686039518</v>
+        <v>1.441734417344174</v>
       </c>
       <c r="J16" t="n">
         <v>59</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.639999866485596</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="I17" t="n">
-        <v>5.319149062089187</v>
+        <v>5.281690300468702</v>
       </c>
       <c r="J17" t="n">
         <v>52</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.720000028610229</v>
+        <v>2.759999990463257</v>
       </c>
       <c r="I19" t="n">
-        <v>8.088235209041814</v>
+        <v>7.971014520296202</v>
       </c>
       <c r="J19" t="n">
         <v>17</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.819999933242798</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2471277837885</v>
+        <v>5.191894910574625</v>
       </c>
       <c r="J21" t="n">
         <v>10</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.099999904632568</v>
+        <v>4.050000190734863</v>
       </c>
       <c r="I23" t="n">
-        <v>3.414634225767048</v>
+        <v>3.456789960659171</v>
       </c>
       <c r="J23" t="n">
         <v>-4</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>9.845000267028809</v>
+        <v>9.927000045776367</v>
       </c>
       <c r="I24" t="n">
-        <v>2.640934412879069</v>
+        <v>2.619119560804495</v>
       </c>
       <c r="J24" t="n">
         <v>-4</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.569999933242798</v>
+        <v>2.594000101089478</v>
       </c>
       <c r="I26" t="n">
-        <v>8.560311506405622</v>
+        <v>8.481109923920211</v>
       </c>
       <c r="J26" t="n">
         <v>-4</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6.414999961853027</v>
+        <v>6.465000152587891</v>
       </c>
       <c r="I28" t="n">
-        <v>3.741231510945699</v>
+        <v>3.712296896140518</v>
       </c>
       <c r="J28" t="n">
         <v>-4</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>8.699999809265137</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5747126562779011</v>
+        <v>0.5617977768886342</v>
       </c>
       <c r="J32" t="n">
         <v>-11</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.759999990463257</v>
+        <v>2.740000009536743</v>
       </c>
       <c r="I33" t="n">
-        <v>5.434782627474683</v>
+        <v>5.474452535690348</v>
       </c>
       <c r="J33" t="n">
         <v>-11</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.119999885559082</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I34" t="n">
-        <v>4.009434178699683</v>
+        <v>4.047619231433834</v>
       </c>
       <c r="J34" t="n">
         <v>-18</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4.449999809265137</v>
+        <v>4.300000190734863</v>
       </c>
       <c r="I35" t="n">
-        <v>1.573033775288176</v>
+        <v>1.627906904535209</v>
       </c>
       <c r="J35" t="n">
         <v>-18</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>32.45000076293945</v>
+        <v>33</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4622496039239303</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="J36" t="n">
         <v>-18</v>
@@ -3587,7 +3587,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3597,14 +3597,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3614,14 +3614,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3631,14 +3631,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3655,7 +3655,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3665,14 +3665,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3682,14 +3682,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3706,7 +3706,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,14 +3733,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3750,14 +3750,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3767,14 +3767,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3784,14 +3784,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3876,7 +3876,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3886,14 +3886,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3920,14 +3920,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3944,7 +3944,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4114,7 +4114,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4131,7 +4131,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4233,7 +4233,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4243,14 +4243,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4260,14 +4260,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4318,7 +4318,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4328,14 +4328,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4362,14 +4362,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4379,14 +4379,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4396,14 +4396,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4420,7 +4420,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4430,14 +4430,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4481,14 +4481,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4498,14 +4498,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4515,14 +4515,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4549,14 +4549,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4573,7 +4573,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4600,14 +4600,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4624,7 +4624,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4634,14 +4634,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4719,14 +4719,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4777,7 +4777,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4794,7 +4794,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4828,7 +4828,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4862,7 +4862,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4906,14 +4906,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4930,7 +4930,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4947,7 +4947,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4964,7 +4964,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5015,7 +5015,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5042,14 +5042,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5066,7 +5066,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5076,14 +5076,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5117,7 +5117,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5134,7 +5134,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5144,14 +5144,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5195,14 +5195,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5212,14 +5212,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5236,7 +5236,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5246,14 +5246,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5270,7 +5270,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5297,14 +5297,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5321,7 +5321,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5348,14 +5348,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5365,14 +5365,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5382,14 +5382,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5399,14 +5399,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5423,7 +5423,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5440,7 +5440,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5450,14 +5450,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5474,7 +5474,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5491,7 +5491,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5535,14 +5535,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5586,14 +5586,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5610,7 +5610,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5627,7 +5627,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5644,7 +5644,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5654,14 +5654,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5671,14 +5671,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5688,14 +5688,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
